--- a/ig/DM_FINESS_New/ValueSet-jdv-disposition-pretherapeutique-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-disposition-pretherapeutique-cisis.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250606103857</t>
+    <t>20250616134739</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-06T10:38:57+01:00</t>
+    <t>2025-06-16T13:47:39+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-disposition-pretherapeutique-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-disposition-pretherapeutique-cisis.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250616134739</t>
+    <t>20250624152100</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>JDV DispositionPretherapeutique CISIS</t>
+    <t>JDV Disposition Pretherapeutique CISIS</t>
   </si>
   <si>
     <t>Status</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-16T13:47:39+01:00</t>
+    <t>2025-06-24T15:21:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-disposition-pretherapeutique-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-disposition-pretherapeutique-cisis.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250624152100</t>
+    <t>20251216141838</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T15:21:00+01:00</t>
+    <t>2025-12-16T14:18:38+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -147,7 +147,7 @@
     <t>233428003</t>
   </si>
   <si>
-    <t>thrombolyse d'une veine</t>
+    <t>thrombolyse veineuse</t>
   </si>
   <si>
     <t>43810009</t>
@@ -171,7 +171,7 @@
     <t>héparine</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/terminologie-atc</t>
+    <t>http://www.whocc.no/atc</t>
   </si>
 </sst>
 </file>

--- a/ig/DM_FINESS_New/ValueSet-jdv-disposition-pretherapeutique-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-disposition-pretherapeutique-cisis.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141838</t>
+    <t>20260220142104</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:38+01:00</t>
+    <t>2026-02-20T14:21:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-disposition-pretherapeutique-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-disposition-pretherapeutique-cisis.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142104</t>
+    <t>20260311144903</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:04+01:00</t>
+    <t>2026-03-11T14:49:03+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-disposition-pretherapeutique-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-disposition-pretherapeutique-cisis.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144903</t>
+    <t>20260420150249</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:03+01:00</t>
+    <t>2026-04-20T15:02:49+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-disposition-pretherapeutique-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-disposition-pretherapeutique-cisis.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150249</t>
+    <t>20260619134042</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:49+01:00</t>
+    <t>2026-06-19T13:40:42+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
